--- a/content/Question Bank/MCQ/Unit 4 - Looping/Unit 4 - Looping - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 4 - Looping/Unit 4 - Looping - MCQ.xlsx
@@ -751,11 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>```python
+          <t>A word-game app reveals a secret word one letter at a time as a hint animation.
+```python
 for letter in "Code":
     print(letter)
 ```
-What does this print?</t>
+What does this print as the app reveals the word letter by letter?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -989,7 +990,8 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Why would a programmer use `enumerate(names)` instead of just for name in names?</t>
+          <t>A contact-list app needs to display each name in a list alongside its position number, like "1. Asha", "2. Ravi".
+Why would a programmer use `enumerate(names)` instead of just for name in names?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1067,13 +1069,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>```python
+          <t>A raffle app skips the unlucky number 3 while announcing ticket numbers one by one.
+```python
 for number in range(1, 6):
     if number == 3:
         continue
     print(number)
 ```
-What is printed?</t>
+What does the app print as it announces the ticket numbers?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1151,13 +1154,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>```python
+          <t>A terminal-based game renders a small triangular level map using rows of stars.
+```python
 for row in range(1, 3):
     for star in range(row):
         print("*", end="")
     print()
 ```
-What is printed?</t>
+What does this print on the screen?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1313,7 +1317,8 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>```python
+          <t>A ticket-counter display is supposed to count down remaining seats as customers check in.
+```python
 count = 1
 while count &lt;= 5:
     print(count)
@@ -1497,7 +1502,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What problem do loops solve that plain sequential code cannot solve well?</t>
+          <t>A gradebook app must print a report card line for every student in a class of 200, and the class size can change each term.
+What problem do loops solve that plain sequential code cannot solve well?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1653,7 +1659,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What are the three essential parts of the while loop counter pattern?</t>
+          <t>A step-counter app needs to keep adding to a daily step total until the user hits their goal.
+What are the three essential parts of the while loop counter pattern?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1976,7 +1983,8 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Why is a for loop considered safer than a while loop for a known fixed number of repetitions?</t>
+          <t>A delivery-tracking app needs to process exactly 12 monthly shipment records.
+Why is a for loop considered safer than a while loop for a known fixed number of repetitions?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2054,7 +2062,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What numbers does `range(1, 6)` produce?</t>
+          <t>A quiz app needs to generate the five question numbers 1 through 5 for a short round.
+What numbers does `range(1, 6)` produce?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2399,7 +2408,8 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Why does `range(1, 6)` stop at 5 instead of 6?</t>
+          <t>A quiz app generates question numbers for a 5-question round using `range(1, 6)`.
+Why does `range(1, 6)` stop at 5 instead of 6?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2477,7 +2487,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>How many values does `range(2, 20, 3)` produce?</t>
+          <t>A playlist shuffler samples track slots using `range(2, 20, 3)` to pick evenly spaced positions.
+How many values does `range(2, 20, 3)` produce?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2716,7 +2727,8 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which statement correctly distinguishes break, continue, and the loop-else clause?</t>
+          <t>A warehouse scanner script processes items in a bin and must decide when to stop scanning and how to skip damaged items.
+Which statement correctly distinguishes break, continue, and the loop-else clause?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3387,7 +3399,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What does it mean for one loop to be 'nested' inside another?</t>
+          <t>A seating-chart app arranges students into rows and columns using one loop inside another.
+What does it mean for one loop to be 'nested' inside another?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3465,7 +3478,8 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>If an outer loop runs 5 times and its inner loop runs 6 times on every single pass, how many total times does the inner block execute?</t>
+          <t>A theater booking system checks every seat in every row before confirming availability.
+If an outer loop runs 5 times and its inner loop runs 6 times on every single pass, how many total times does the inner block execute?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3885,7 +3899,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A developer nests two loops, each running 1000 times, to compare every item in a list against every other item. Why should this be approached carefully on large data?</t>
+          <t>A recommendation engine compares every product in a 1000-item catalog against every other product to find similar pairs, using two nested loops that each run 1000 times.
+Why should this be approached carefully on large data?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">

--- a/content/Question Bank/MCQ/Unit 4 - Looping/Unit 4 - Looping - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 4 - Looping/Unit 4 - Looping - MCQ.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Python - MCQ - 4.1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Python - MCQ - 4.2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Python - MCQ - 4.3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Python - MCQ - 4.4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 4.1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 4.2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 4.3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 4.4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -643,26 +643,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>A for loop, since the items to visit are already known</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>A while loop, since you cannot know the count</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>An if-elif chain checking each name</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>Neither of these, this genuinely needs recursion</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>An if-elif chain checking each name</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>A for loop, since the items to visit are already known</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>A while loop, since you cannot know the count</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -809,17 +809,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>'Code' printed once</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>An error, strings cannot be looped over</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>4 4 4 4</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>'Code' printed once</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>An error, strings cannot be looped over</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -960,26 +960,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>Because for loops technically cannot make use of the `input()` function at all</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Because email addresses are always stored as plain text string values</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Because the number of repetitions is unknown in advance and depends on a changing condition</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>Because while loops are always noticeably faster to execute than for loops</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Because for loops technically cannot make use of the `input()` function at all</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Because the number of repetitions is unknown in advance and depends on a changing condition</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1039,26 +1039,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>To sort the list into order before looping over it each time</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>To get both the index/position and the item together on each pass</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>To automatically reverse the order of the list</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>To skip over every other item in the sequence</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>To automatically reverse the order of the list</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>To sort the list into order before looping over it</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1124,26 +1124,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>1 2 3 4 5</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1 2 4 5</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1 2 3</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>Nothing</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1 2 3 4 5</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1 2 3</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>1 2 4 5</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1292,17 +1292,17 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>Python automatically prevents this kind of infinite loop</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>No danger, balance always decreases</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>The loop will raise an error if withdrawal is 0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Python automatically prevents this kind of infinite loop</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1371,26 +1371,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>It raises a syntax error before the code ever runs</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>It prints nothing at all because count starts out wrong</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>It prints the numbers 1 through 5 and then stops as expected</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>It prints 1 forever, because count is never updated inside the loop</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>It prints nothing at all because count starts out wrong</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>It raises a syntax error before the code ever runs</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>They make certain variables become permanently unchangeable</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>They make programs run successfully without any user input at all</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>They completely remove the need for any conditions in the code</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>They let you write an action once and have Python repeat it automatically</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>They make certain variables become permanently unchangeable</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>They make programs run successfully without any user input at all</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1629,26 +1629,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>while count &lt; 10:</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>loop while count &lt; 10:</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>while (count &lt; 10) do:</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>while count &lt; 10 then</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>while count &lt; 10:</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>while (count &lt; 10) do:</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1708,26 +1708,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>Initialize the counter, test it in the condition, update it inside the loop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Define a function, call it once, then return a value from it</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Open a file, read its entire contents, then close it properly</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>Import a module, declare a variable, then print its value</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Open a file, read its entire contents, then close it properly</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Define a function, call it once, then return a value from it</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Initialize the counter, test it in the condition, update it inside the loop</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1786,26 +1786,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>Python technically does not allow more than ten print statements</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>It always runs measurably slower than any loop would</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>It technically uses far more memory than any loop ever could</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>It always runs measurably slower than any loop would</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>A stray typo or miscount can easily hide among many near-identical lines</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Python technically does not allow more than ten print statements</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -1880,16 +1880,16 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
+          <t>1 2 3</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>Nothing</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>1 2 3</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1953,17 +1953,17 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>The search pattern used for scanning through a list</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>The sentinel pattern, stopping when a special signal value appears</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>An infinite loop that genuinely has no way to ever stop</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>The sentinel pattern, stopping when a special signal value appears</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>The search pattern used for scanning through a list</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -2037,17 +2037,17 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>A for loop can never be stopped early once it has already started running all the way through its passes</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>A for loop handles its own counting, removing the risk of forgetting to update a counter and looping forever</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>A for loop will always run measurably and noticeably faster on every single machine</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>A for loop handles its own counting, removing the risk of forgetting to update a counter and looping forever</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>A for loop can never be stopped early once it has already started running its passes</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -2111,14 +2111,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>2, 3, 4, 5, 6</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>1, 2, 3, 4, 5</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2, 3, 4, 5, 6</t>
-        </is>
-      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>0, 1, 2, 3, 4, 5</t>
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -2195,26 +2195,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>Three times</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>Four times</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Three times</t>
-        </is>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>It never stops</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>Five times</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>It never stops</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2277,26 +2277,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>0 2 4 6 8</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0 2 4 6 8 10</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2 4 6 8 10</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>0 1 2 3 4 5 6 7 8 9</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0 2 4 6 8</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0 2 4 6 8 10</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2 4 6 8 10</t>
-        </is>
-      </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2536,22 +2536,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>Seven values</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Six values</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Five values</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>Eighteen values</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Six values</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Seven values</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Five values</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -2614,26 +2614,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>It adds unnecessary manual counter bookkeeping and risk of mistakes that `range(10)` avoids</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>for loops are technically incapable of performing any real calculations</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>while loops execute in a fundamentally different order than for loops always do</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>while loops technically cannot be made to repeat exactly 10 times</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>It adds unnecessary manual counter bookkeeping and risk of mistakes that `range(10)` avoids</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>while loops execute in a fundamentally different order than for loops do</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>for loops are technically incapable of performing any real calculations</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2697,26 +2697,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>Hi Asha only</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Hi names printed</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Hi Asha then Hi Ravi</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>Hi Ravi then Hi Asha</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Hi names printed</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Hi Asha only</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Hi Asha then Hi Ravi</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2776,17 +2776,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>break and continue essentially do exactly the same thing in every situation</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>continue always stops the entire loop immediately, exactly like break does</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>else always runs after every single loop finishes, no matter what happens inside it</t>
-        </is>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>break and continue essentially do exactly the same thing in every situation</t>
+          <t>else always runs after every single loop finishes, no matter what happens inside it every time</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -2864,17 +2864,17 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>Sam 1 then Lee 2</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1 Sam then 2 Lee</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>0 Sam then 1 Lee</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1 Sam then 2 Lee</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Sam 1 then Lee 2</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -2954,16 +2954,16 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -3028,26 +3028,26 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3106,26 +3106,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>Index-based loops technically cannot make any use of the print function at all, ever</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>It adds needless complexity and index-error risk compared to iterating directly over the items</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>It is functionally completely impossible to write in Python at all</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>It would technically only ever work correctly with strings, never with lists</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>It adds needless complexity and index-error risk compared to iterating directly over the items</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Index-based loops technically cannot make any use of the print function at all</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -3189,17 +3189,17 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>Nothing changes at all, since continue and break are interchangeable</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>The loop stops immediately in this case, exactly like break would</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>The program immediately raises a runtime error instead</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Nothing changes at all, since continue and break are interchangeable</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>The loop stops immediately in this case, exactly like break would</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -3369,26 +3369,26 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>Nothing at all would change in the printed output</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Each '#' would print on its own separate line instead of forming one row</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>The pattern would print all hashes on a single line with no rows</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>The loop would immediately throw a `TypeError` when it runs</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Nothing at all would change in the printed output</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Each '#' would print on its own separate line instead of forming one row</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -3448,26 +3448,26 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>Two loops that simply run one after the other, not nested inside each other</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>A loop placed inside the body of another loop, running fully for each outer pass</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Two loops that run one after the other, not inside each other</t>
-        </is>
-      </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>A loop with two separate conditions joined together by and</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>A loop that calls itself recursively instead of nesting</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>A loop with two separate conditions joined together by and</t>
-        </is>
-      </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -3527,26 +3527,26 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3612,26 +3612,26 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>The counting pattern, `evens = 3`</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>The sum pattern, `evens = 6`</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>The search pattern, `evens = True`</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>The max pattern, `evens = 9`</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>The search pattern, `evens = True`</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>The counting pattern, `evens = 3`</t>
-        </is>
-      </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3699,26 +3699,26 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>Found</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Nothing</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>Both Found and Not found</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Found</t>
-        </is>
-      </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3784,26 +3784,26 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -3869,26 +3869,26 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -3953,21 +3953,21 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Nested loops technically cannot make use of the `range()` function</t>
+          <t>The total work multiplies, so it can grow very large very quickly as data size increases</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>The total work multiplies, so it can grow very large very quickly as data size increases</t>
+          <t>Nested loops will always crash outright on data over 100 items</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nested loops will always crash outright on data over 100 items</t>
+          <t>Nested loops technically cannot make use of the `range()` function at any level</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -4035,26 +4035,26 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>It is technically required syntax for every single for loop written in Python</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>It is not actually necessary at all and serves absolutely no real purpose in this situation</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>It somehow makes the entire loop run measurably and noticeably faster</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>It preserves whether the target was actually found, since break alone leaves no record afterward</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>It is not actually necessary at all and serves absolutely no real purpose here</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>It is technically required syntax for every single for loop written in Python</t>
-        </is>
-      </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -4113,26 +4113,26 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>It incorrectly reports 0 as the largest value, since no negative number exceeds 0</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>It correctly reports -9 as being the largest value in the list</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>It immediately raises an `IndexError` the moment it runs</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>It works correctly no matter what the starting value happens to be</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>It incorrectly reports 0 as the largest value, since no negative number exceeds 0</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>It correctly reports -9 as being the largest value in the list</t>
+          <t>It works correctly no matter what the starting value happens to be set to</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/content/Question Bank/MCQ/Unit 4 - Looping/Unit 4 - Looping - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 4 - Looping/Unit 4 - Looping - MCQ.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 4" sheetId="1" r:id="Rbeaf4f365a8d4e58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 4" sheetId="1" r:id="Rac999c01ea394013"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -281,7 +281,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="70" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="74" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="70" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
@@ -292,10 +292,10 @@
     <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="36" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="36" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="36" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="36" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="38" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="38" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="38" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="38" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="10" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -352,13 +352,13 @@
         <x:v>answer</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="2" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A2" s="5" t="str">
         <x:v>Python - MCQ - 4.1.1</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
         <x:v>A school attendance system has a list of roll numbers for today's class. It must mark attendance once for each roll number already present in the list.
-Which loop is the best fit for this requirement?</x:v>
+Which loop should the system use to process each roll number cleanly?</x:v>
       </x:c>
       <x:c r="C2" s="5" t="str">
         <x:v>A for loop is best when the program already has a sequence of items to visit. Here, the roll-number list decides exactly what must be processed, so Python can take one roll number at a time without a manually managed counter.</x:v>
@@ -404,13 +404,13 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="3" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A3" s="5" t="str">
         <x:v>Python - MCQ - 4.1.2</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
         <x:v>A cafe billing app keeps accepting item names until the cashier types `done`.
-Which loop condition best matches this sentinel-based requirement?</x:v>
+The cashier has not fixed the number of items in advance. Which loop condition should the billing app use to keep accepting items until the stop word appears?</x:v>
       </x:c>
       <x:c r="C3" s="5" t="str">
         <x:v>A sentinel loop repeats until a special value appears. The loop should continue while the item is not `done` and stop as soon as `done` is entered.</x:v>
@@ -456,13 +456,13 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="4" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A4" s="5" t="str">
         <x:v>Python - MCQ - 4.1.3</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
         <x:v>A quiz app must display question numbers 1, 2, 3, 4, and 5 before starting a round.
-Which line should replace the blank?
+Which line should replace the blank so the app shows exactly those five question numbers?
 ```python
 for q_no in ______:
     print(q_no)
@@ -512,13 +512,13 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="5" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A5" s="5" t="str">
         <x:v>Python - MCQ - 4.1.4</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>A contact app must show each contact with a serial number like `1. Asha`, `2. Ravi`, and `3. Mina`.
-Which concept makes this cleanest?</x:v>
+        <x:v>A contact app must show each contact with a serial number, such as `1. Asha`, `2. Ravi`, and `3. Mina`.
+Which loop technique should the app use so each contact is shown with the correct serial number?</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
         <x:v>`enumerate()` gives both the index/position and the item during each loop pass. With `start=1`, the numbering matches the user-facing serial numbers.</x:v>
@@ -564,12 +564,12 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="6" ht="132" hidden="0" customHeight="1">
       <x:c r="A6" s="5" t="str">
         <x:v>Python - MCQ - 4.1.5</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>An order system skips unavailable items.
+        <x:v>An order system skips items that are marked as unavailable.
 ```python
 items = ["tea", "sold out", "coffee"]
 for item in items:
@@ -577,7 +577,7 @@
         continue
     print(item)
 ```
-What is printed?</x:v>
+A customer views the available-item list. Which items will the system show to the customer?</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
         <x:v>`continue` skips only the current iteration. The sold-out item is skipped, but the loop continues and prints tea and coffee.</x:v>
@@ -623,12 +623,12 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="7" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A7" s="5" t="str">
         <x:v>Python - MCQ - 4.1.6</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
-        <x:v>A scholarship checker stops when it finds the first score of 90 or above.
+        <x:v>A scholarship checker scans scores in order and should stop as soon as it finds the first score of 90 or above.
 ```python
 scores = [72, 88, 91, 95]
 for score in scores:
@@ -636,7 +636,7 @@
         print(score)
         break
 ```
-What is printed?</x:v>
+Which score will the checker display as the first qualifying score?</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
         <x:v>The loop checks scores in order. 72 and 88 do not qualify. 91 qualifies, so it is printed and `break` stops the loop before 95 is checked.</x:v>
@@ -682,12 +682,12 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="8" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A8" s="5" t="str">
         <x:v>Python - MCQ - 4.1.7</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
-        <x:v>A search program reports when an item is missing.
+        <x:v>A search program checks a stationery box for an eraser.
 ```python
 target = "eraser"
 for item in ["pen", "pencil", "scale"]:
@@ -697,7 +697,7 @@
 else:
     print("Missing")
 ```
-What is printed?</x:v>
+The box does not contain an eraser. What message will the search program show?</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
         <x:v>The target is never found, so `break` never runs. A loop's `else` block runs only when the loop finishes without a break, so it prints Missing.</x:v>
@@ -743,19 +743,19 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="9" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A9" s="5" t="str">
         <x:v>Python - MCQ - 4.1.8</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>A pattern-printing program creates a small triangle.
+        <x:v>A pattern-printing tool creates a small triangle for a terminal display.
 ```python
 for row in range(1, 4):
     for col in range(row):
         print("*", end="")
     print()
 ```
-What is printed?</x:v>
+When the display is generated, which star pattern will appear on the screen?</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
         <x:v>The outer loop uses row values 1, 2, and 3. The inner loop prints that many stars on each row, and the final `print()` moves to the next line.</x:v>
@@ -807,18 +807,18 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="10" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A10" s="5" t="str">
         <x:v>Python - MCQ - 4.1.9</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
-        <x:v>A retry loop currently gives four attempts by mistake.
+        <x:v>A retry screen should allow exactly three attempts, but the current loop allows one extra attempt.
 ```python
 attempts = 0
 while attempts &lt;= 3:
     attempts += 1
 ```
-What change gives exactly three attempts?</x:v>
+Which change should the developer make so the retry screen allows exactly three attempts?</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
         <x:v>Starting from 0, the condition `attempts &lt; 3` runs for attempts 0, 1, and 2. The original `&lt;= 3` runs one extra time.</x:v>
@@ -864,13 +864,13 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="11" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A11" s="5" t="str">
         <x:v>Python - MCQ - 4.1.10</x:v>
       </x:c>
       <x:c r="B11" s="5" t="str">
-        <x:v>A weather app must find the highest temperature in a list that may contain only negative values.
-Which initialization is safest?</x:v>
+        <x:v>A weather app must find the highest temperature in a list, and some cities may have only negative temperatures.
+Which initialization lets the app still find the correct highest temperature for a list like `[-5, -2, -9]`?</x:v>
       </x:c>
       <x:c r="C11" s="5" t="str">
         <x:v>Starting with the first actual list value avoids assuming that the maximum is non-negative. Initializing to 0 would fail for all-negative lists.</x:v>
@@ -916,7 +916,7 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="12" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A12" s="5" t="str">
         <x:v>Python - MCQ - 4.2.1</x:v>
       </x:c>
@@ -927,7 +927,7 @@
 for ch in code:
     print(ch)
 ```
-What is printed?</x:v>
+When the badge code is revealed character by character, what will the printer output?</x:v>
       </x:c>
       <x:c r="C12" s="5" t="str">
         <x:v>Strings are sequences, so the loop visits each character in order: A, then I, then 2. Each print call uses a new line by default.</x:v>
@@ -973,7 +973,7 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="13" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A13" s="5" t="str">
         <x:v>Python - MCQ - 4.2.2</x:v>
       </x:c>
@@ -985,7 +985,7 @@
     print(count)
     count += 1
 ```
-Why does this code fail before it can print anything?</x:v>
+Before the ticket counter can run, what problem will Python report?</x:v>
       </x:c>
       <x:c r="C13" s="5" t="str">
         <x:v>The `while` statement must end with a colon. Because the colon after `count &lt;= 3` is missing, Python raises a syntax error before running the loop body.</x:v>
@@ -1031,7 +1031,7 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="14" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A14" s="5" t="str">
         <x:v>Python - MCQ - 4.2.3</x:v>
       </x:c>
@@ -1043,7 +1043,7 @@
     print("Try", attempt)
     attempt += 1
 ```
-How many times does the loop body run?</x:v>
+How many attempt messages will the retry screen show?</x:v>
       </x:c>
       <x:c r="C14" s="5" t="str">
         <x:v>The loop runs for attempt values 1, 2, and 3. After the third run, attempt becomes 4, making `attempt &lt;= 3` false.</x:v>
@@ -1089,7 +1089,7 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="15" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A15" s="5" t="str">
         <x:v>Python - MCQ - 4.2.4</x:v>
       </x:c>
@@ -1099,7 +1099,7 @@
 for slot in range(5, 5):
     print(slot)
 ```
-What happens?</x:v>
+When the scheduler runs, what slot numbers will it show?</x:v>
       </x:c>
       <x:c r="C15" s="5" t="str">
         <x:v>`range(5, 5)` is empty because the start and stop are the same, and the stop value is excluded. The loop body never runs.</x:v>
@@ -1145,7 +1145,7 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="16" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A16" s="5" t="str">
         <x:v>Python - MCQ - 4.2.5</x:v>
       </x:c>
@@ -1156,7 +1156,7 @@
 while seconds &gt; 0:
     print(seconds)
 ```
-Which line should be added inside the loop to make it stop correctly?</x:v>
+Which line should be added inside the loop so the countdown shows 3, 2, 1 and then stops?</x:v>
       </x:c>
       <x:c r="C16" s="5" t="str">
         <x:v>The loop condition depends on `seconds`, so `seconds` must move toward 0 on every pass. Subtracting 1 after printing gives 3, 2, 1 and then stops.</x:v>
@@ -1202,7 +1202,7 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="17" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A17" s="5" t="str">
         <x:v>Python - MCQ - 4.2.6</x:v>
       </x:c>
@@ -1212,7 +1212,7 @@
 for n in range(0, 10, 2):
     print(n)
 ```
-The requirement changes: print even numbers from 10 down to 2. Which range should be used?</x:v>
+The requirement changes: the display should show even numbers from 10 down to 2. Which `range()` call should the display use?</x:v>
       </x:c>
       <x:c r="C17" s="5" t="str">
         <x:v>For a countdown, the step must be negative. `range(10, 1, -2)` produces 10, 8, 6, 4, 2 because it stops before 1.</x:v>
@@ -1258,19 +1258,19 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="18" ht="132" hidden="0" customHeight="1">
       <x:c r="A18" s="5" t="str">
         <x:v>Python - MCQ - 4.2.7</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
-        <x:v>A developer wrote this repeated code.
+        <x:v>A developer wrote this repeated backup message by copying the same line four times.
 ```python
 print("Backup started")
 print("Backup started")
 print("Backup started")
 print("Backup started")
 ```
-Which replacement is cleanest if the message must be printed exactly four times?</x:v>
+Which replacement should the developer use so the backup tool shows the same message exactly four times with cleaner code?</x:v>
       </x:c>
       <x:c r="C18" s="5" t="str">
         <x:v>A for loop with `range(4)` expresses four repetitions directly and avoids copying the same print statement multiple times.</x:v>
@@ -1316,7 +1316,7 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="19" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A19" s="5" t="str">
         <x:v>Python - MCQ - 4.2.8</x:v>
       </x:c>
@@ -1328,7 +1328,7 @@
     print(checkpoint)
     checkpoint += 1
 ```
-What is printed?</x:v>
+When the progress indicator runs, which checkpoint numbers will appear?</x:v>
       </x:c>
       <x:c r="C19" s="5" t="str">
         <x:v>The loop runs for checkpoint values 0, 1, 2, and 3. When checkpoint becomes 4, the condition `checkpoint &lt; 4` becomes false.</x:v>
@@ -1374,17 +1374,17 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="20" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A20" s="5" t="str">
         <x:v>Python - MCQ - 4.2.9</x:v>
       </x:c>
       <x:c r="B20" s="5" t="str">
-        <x:v>A login script is written as follows.
+        <x:v>A login script checks the entered PIN before asking the user for input.
 ```python
 while pin != "1234":
     pin = input("PIN: ")
 ```
-Why can this code fail before asking for input?</x:v>
+Why can this login script fail before the first PIN prompt appears?</x:v>
       </x:c>
       <x:c r="C20" s="5" t="str">
         <x:v>The condition checks `pin` before any value has been assigned to it. `pin` should be initialized before the while loop, such as `pin = ""`.</x:v>
@@ -1436,7 +1436,7 @@
       </x:c>
       <x:c r="B21" s="5" t="str">
         <x:v>A security app should allow at most 3 wrong password attempts.
-Which version correctly moves the loop toward stopping?</x:v>
+Which version correctly updates the attempt count so the security app can stop after the third wrong attempt?</x:v>
       </x:c>
       <x:c r="C21" s="5" t="str">
         <x:v>The safe version initializes attempts, checks the limit, and increments attempts inside the loop. Without the increment, the loop may never reach the stopping condition.</x:v>
@@ -1491,7 +1491,7 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="22" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A22" s="5" t="str">
         <x:v>Python - MCQ - 4.2.11</x:v>
       </x:c>
@@ -1503,7 +1503,7 @@
 while stock &gt; 0:
     stock = stock - packed
 ```
-What is the risk in this code?</x:v>
+When this stock-checking loop runs, what problem can occur?</x:v>
       </x:c>
       <x:c r="C22" s="5" t="str">
         <x:v>Since `packed` is 0, `stock` never changes from 10. The condition remains true forever, causing an infinite loop.</x:v>
@@ -1549,7 +1549,7 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="132" hidden="0" customHeight="1">
+    <x:row r="23" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A23" s="5" t="str">
         <x:v>Python - MCQ - 4.2.12</x:v>
       </x:c>
@@ -1563,7 +1563,7 @@
     total += scores[i]
     i += 1
 ```
-What is the final value of `total`?</x:v>
+After all survey scores are processed, what total will the system store?</x:v>
       </x:c>
       <x:c r="C23" s="5" t="str">
         <x:v>The loop adds scores[0], scores[1], and scores[2]: 4 + 0 + 5. The final total is 9.</x:v>
@@ -1609,13 +1609,13 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="24" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A24" s="5" t="str">
         <x:v>Python - MCQ - 4.2.13</x:v>
       </x:c>
       <x:c r="B24" s="5" t="str">
-        <x:v>A form should keep asking for age until the value is between 18 and 60, inclusive.
-Which condition should be used in the while loop?</x:v>
+        <x:v>A registration form should keep asking for age until the value is between 18 and 60, inclusive.
+Which loop condition should the form use while the entered age is still invalid?</x:v>
       </x:c>
       <x:c r="C24" s="5" t="str">
         <x:v>The loop should continue while the age is invalid. Ages below 18 or above 60 are invalid, so `age &lt; 18 or age &gt; 60` is the correct condition.</x:v>
@@ -1661,13 +1661,13 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="25" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A25" s="5" t="str">
         <x:v>Python - MCQ - 4.2.14</x:v>
       </x:c>
       <x:c r="B25" s="5" t="str">
         <x:v>A chatbot keeps reading messages until the user types `bye`. The number of messages is not known beforehand.
-Which loop pattern is being used?</x:v>
+Which loop pattern is the chatbot using to decide when the conversation should stop?</x:v>
       </x:c>
       <x:c r="C25" s="5" t="str">
         <x:v>This is a sentinel-controlled loop. It stops when a special signal value, `bye`, appears rather than after a fixed count.</x:v>
@@ -1713,7 +1713,7 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="26" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A26" s="5" t="str">
         <x:v>Python - MCQ - 4.2.15</x:v>
       </x:c>
@@ -1725,7 +1725,7 @@
     print(n)
     n += 1
 ```
-Is the claim correct?</x:v>
+When the ticket display runs, is the developer's claim correct?</x:v>
       </x:c>
       <x:c r="C26" s="5" t="str">
         <x:v>The condition is `n &lt; 5`, so the loop prints 1, 2, 3, and 4 only. To include 5, the condition would need to be `n &lt;= 5`.</x:v>
@@ -1771,7 +1771,7 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="27" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A27" s="5" t="str">
         <x:v>Python - MCQ - 4.2.16</x:v>
       </x:c>
@@ -1781,7 +1781,7 @@
 for q in range(1, 6):
     print(q)
 ```
-Why does the app stop at 5 instead of printing 6?</x:v>
+The app shows 1 through 5, but not 6. Why does the question-number display stop before 6?</x:v>
       </x:c>
       <x:c r="C27" s="5" t="str">
         <x:v>`range(start, stop)` includes the start value but excludes the stop value. Therefore, `range(1, 6)` produces 1 through 5.</x:v>
@@ -1827,7 +1827,7 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="28" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A28" s="5" t="str">
         <x:v>Python - MCQ - 4.2.17</x:v>
       </x:c>
@@ -1837,7 +1837,7 @@
 for n in range(10, 0, -3):
     print(n, end=" ")
 ```
-What is printed?</x:v>
+When the countdown display runs, which numbers will appear?</x:v>
       </x:c>
       <x:c r="C28" s="5" t="str">
         <x:v>The range starts at 10 and subtracts 3 each time while staying above 0. It produces 10, 7, 4, and 1.</x:v>
@@ -1883,18 +1883,18 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="29" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A29" s="5" t="str">
         <x:v>Python - MCQ - 4.2.18</x:v>
       </x:c>
       <x:c r="B29" s="5" t="str">
-        <x:v>A developer wants to print each product name, but writes:
+        <x:v>A developer wants to show each product name, but writes:
 ```python
 products = ["pen", "bag", "book"]
 for i in products:
     print(products[i])
 ```
-Why is this wrong?</x:v>
+When the product display runs, why will this code fail?</x:v>
       </x:c>
       <x:c r="C29" s="5" t="str">
         <x:v>In `for i in products`, `i` becomes each product string, such as `"pen"`, not a numeric index. Using a string as a list index causes an error.</x:v>
@@ -1940,18 +1940,18 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="30" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A30" s="5" t="str">
         <x:v>Python - MCQ - 4.2.19</x:v>
       </x:c>
       <x:c r="B30" s="5" t="str">
         <x:v>A leaderboard should display ranks starting from 1.
-Which line should replace the blank?
 ```python
 players = ["Asha", "Ravi"]
 for rank, player in ______:
     print(rank, player)
-```</x:v>
+```
+Which line should replace the blank so the leaderboard shows each player with the correct rank?</x:v>
       </x:c>
       <x:c r="C30" s="5" t="str">
         <x:v>`enumerate(players, start=1)` produces pairs `(1, "Asha")` and `(2, "Ravi")`, giving both the rank and the player.</x:v>
@@ -1997,17 +1997,17 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="31" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A31" s="5" t="str">
         <x:v>Python - MCQ - 4.2.20</x:v>
       </x:c>
       <x:c r="B31" s="5" t="str">
-        <x:v>A developer writes:
+        <x:v>A developer writes this loop to display names:
 ```python
 for i in range(len(names)):
     print(names[i])
 ```
-If the index is not needed, which replacement is cleaner?</x:v>
+If the app only needs each name and does not need the index, which replacement is cleaner?</x:v>
       </x:c>
       <x:c r="C31" s="5" t="str">
         <x:v>When only the item is needed, direct iteration is clearer and avoids unnecessary index handling.</x:v>
@@ -2057,24 +2057,24 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="132" hidden="0" customHeight="1">
+    <x:row r="32" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A32" s="5" t="str">
         <x:v>Python - MCQ - 4.2.21</x:v>
       </x:c>
       <x:c r="B32" s="5" t="str">
-        <x:v>A data-cleaning loop should keep only positive numbers.
+        <x:v>A data-cleaning loop should add only positive numbers to a running total.
 ```python
 values = [3, -1, 4]
-clean = []
+total = 0
 for v in values:
     if v &lt; 0:
         continue
-    clean.append(v)
-```
-What is the final value of `clean`?</x:v>
+    total = total + v
+```
+After the loop finishes, what total will the program store?</x:v>
       </x:c>
       <x:c r="C32" s="5" t="str">
-        <x:v>When v is -1, `continue` skips the append. The positive values 3 and 4 are appended, so clean becomes `[3, 4]`.</x:v>
+        <x:v>The loop adds 3, skips -1 because `continue` jumps to the next iteration, and then adds 4. The final total is 7.</x:v>
       </x:c>
       <x:c r="D32" s="5" t="n">
         <x:v>1</x:v>
@@ -2102,22 +2102,22 @@
       </x:c>
       <x:c r="L32" s="5"/>
       <x:c r="M32" s="5" t="str">
-        <x:v>[3, -1, 4]</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N32" s="5" t="str">
-        <x:v>[-1]</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="O32" s="5" t="str">
-        <x:v>[3, 4]</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="P32" s="5" t="str">
-        <x:v>[]</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Q32" s="5" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="132" hidden="0" customHeight="1">
+    <x:row r="33" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A33" s="5" t="str">
         <x:v>Python - MCQ - 4.2.22</x:v>
       </x:c>
@@ -2131,7 +2131,7 @@
         valid = False
         break
 ```
-Does this code meet the requirement?</x:v>
+Does this validator correctly reject the batch when it reaches the first negative quantity?</x:v>
       </x:c>
       <x:c r="C33" s="5" t="str">
         <x:v>Yes. The loop checks quantities one by one, sets `valid` to False at the first negative value, and uses `break` to stop checking the rest.</x:v>
@@ -2177,13 +2177,13 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="34" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A34" s="5" t="str">
         <x:v>Python - MCQ - 4.2.23</x:v>
       </x:c>
       <x:c r="B34" s="5" t="str">
         <x:v>A seating chart checks 3 rows, and each row has 4 seats.
-If the outer loop runs 3 times and the inner loop runs 4 times for each outer pass, how many seat checks happen?</x:v>
+If the outer loop checks each row and the inner loop checks each seat in that row, how many seat checks will the seating-chart system perform?</x:v>
       </x:c>
       <x:c r="C34" s="5" t="str">
         <x:v>Nested loop work multiplies: 3 outer passes x 4 inner passes = 12 total checks.</x:v>
@@ -2229,12 +2229,12 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="35" ht="184.8000030517578" hidden="0" customHeight="1">
       <x:c r="A35" s="5" t="str">
         <x:v>Python - MCQ - 4.2.24</x:v>
       </x:c>
       <x:c r="B35" s="5" t="str">
-        <x:v>A developer wants this output:
+        <x:v>A developer wants this two-row pattern on a terminal screen:
 ```text
 ***
 ***
@@ -2246,7 +2246,7 @@
         print("*", end="")
 print()
 ```
-What is wrong?</x:v>
+When the terminal pattern is generated, why will the rows not appear correctly?</x:v>
       </x:c>
       <x:c r="C35" s="5" t="str">
         <x:v>The newline `print()` is outside the outer loop, so it runs only once after all stars are printed. It should be indented inside the outer loop, after the inner loop.</x:v>
@@ -2292,7 +2292,7 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="36" ht="132" hidden="0" customHeight="1">
       <x:c r="A36" s="5" t="str">
         <x:v>Python - MCQ - 4.2.25</x:v>
       </x:c>
@@ -2305,7 +2305,7 @@
     if amount &gt; 0:
         total += amount
 ```
-What is the final value of `total`?</x:v>
+After the donation list is processed, what total will the app store?</x:v>
       </x:c>
       <x:c r="C36" s="5" t="str">
         <x:v>Only positive amounts are added. The loop adds 100 and 50, while -20 and 0 are ignored, so the total is 150.</x:v>
@@ -2351,13 +2351,13 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="37" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A37" s="5" t="str">
         <x:v>Python - MCQ - 4.2.26</x:v>
       </x:c>
       <x:c r="B37" s="5" t="str">
-        <x:v>A multiplication-table app should print rows for 1, 2, and 3 and columns for 1, 2, and 3.
-Which nested loop header pair is correct?</x:v>
+        <x:v>A multiplication-table app should generate rows for 1, 2, and 3 and columns for 1, 2, and 3.
+Which nested-loop header pair should the app use to generate the 3 by 3 table?</x:v>
       </x:c>
       <x:c r="C37" s="5" t="str">
         <x:v>`range(1, 4)` produces 1, 2, and 3. Using it for both row and column creates the required 3 by 3 table.</x:v>
@@ -2407,12 +2407,12 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="38" ht="132" hidden="0" customHeight="1">
       <x:c r="A38" s="5" t="str">
         <x:v>Python - MCQ - 4.2.27</x:v>
       </x:c>
       <x:c r="B38" s="5" t="str">
-        <x:v>A program finds the largest number like this:
+        <x:v>A program tries to find the largest number in an empty list.
 ```python
 numbers = []
 largest = numbers[0]
@@ -2420,7 +2420,7 @@
     if n &gt; largest:
         largest = n
 ```
-What happens for the empty list?</x:v>
+When the program starts processing this empty list, what will happen?</x:v>
       </x:c>
       <x:c r="C38" s="5" t="str">
         <x:v>The code tries to access `numbers[0]`, but an empty list has no first element. Python raises an IndexError before the loop starts.</x:v>
@@ -2466,13 +2466,13 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="39" ht="66" hidden="0" customHeight="1">
       <x:c r="A39" s="5" t="str">
         <x:v>Python - MCQ - 4.2.28</x:v>
       </x:c>
       <x:c r="B39" s="5" t="str">
-        <x:v>A comparison tool checks every user against every course using nested loops. There are 100 users and 100 courses.
-How many comparisons are made?</x:v>
+        <x:v>A course recommendation tool compares every user against every course. There are 100 users and 100 courses.
+If the tool uses one loop for users and a nested loop for courses, how many comparisons will it perform?</x:v>
       </x:c>
       <x:c r="C39" s="5" t="str">
         <x:v>The inner loop runs 100 times for each of the 100 users, so the total is 100 x 100 = 10,000 comparisons.</x:v>
@@ -2518,19 +2518,19 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="40" ht="132" hidden="0" customHeight="1">
       <x:c r="A40" s="5" t="str">
         <x:v>Python - MCQ - 4.2.29</x:v>
       </x:c>
       <x:c r="B40" s="5" t="str">
-        <x:v>A pattern currently grows by row.
+        <x:v>A terminal pattern currently grows by row.
 ```python
 for row in range(1, 4):
     for col in range(row):
         print("#", end="")
     print()
 ```
-The new requirement is to print exactly 3 hashes on every row for 3 rows. What should change?</x:v>
+The new requirement is to show exactly 3 hashes on every row for 3 rows. What should the developer change?</x:v>
       </x:c>
       <x:c r="C40" s="5" t="str">
         <x:v>The current inner range depends on `row`, so the width changes. Using `range(3)` for the inner loop prints exactly three hashes on every row.</x:v>
@@ -2576,7 +2576,7 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="132" hidden="0" customHeight="1">
+    <x:row r="41" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A41" s="5" t="str">
         <x:v>Python - MCQ - 4.2.30</x:v>
       </x:c>
@@ -2590,7 +2590,7 @@
         all_positive = False
         break
 ```
-What is the final value of `all_positive`, and why?</x:v>
+After the payment checker reaches the zero amount, what final value will it store in `all_positive`?</x:v>
       </x:c>
       <x:c r="C41" s="5" t="str">
         <x:v>The loop reaches amount 0, which is not positive. It sets `all_positive` to False and breaks, so the final value is False.</x:v>
@@ -2639,7 +2639,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f2e7e97434d41ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8318f5c331c426e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/content/Question Bank/MCQ/Unit 4 - Looping/Unit 4 - Looping - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 4 - Looping/Unit 4 - Looping - MCQ.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 4" sheetId="1" r:id="R1dfa595974a04008"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 4" sheetId="1" r:id="R4d3313ba56aa42bb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -30,12 +30,22 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -49,7 +59,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="12">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -75,6 +85,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -391,55 +407,55 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" customHeight="1">
-      <x:c r="A1" s="8" t="str">
+      <x:c r="A1" s="11" t="str">
         <x:v>title</x:v>
       </x:c>
-      <x:c r="B1" s="8" t="str">
+      <x:c r="B1" s="11" t="str">
         <x:v>description</x:v>
       </x:c>
-      <x:c r="C1" s="8" t="str">
+      <x:c r="C1" s="11" t="str">
         <x:v>explanation</x:v>
       </x:c>
-      <x:c r="D1" s="8" t="str">
+      <x:c r="D1" s="11" t="str">
         <x:v>score</x:v>
       </x:c>
-      <x:c r="E1" s="8" t="str">
+      <x:c r="E1" s="11" t="str">
         <x:v>status</x:v>
       </x:c>
-      <x:c r="F1" s="8" t="str">
+      <x:c r="F1" s="11" t="str">
         <x:v>difficulty</x:v>
       </x:c>
-      <x:c r="G1" s="8" t="str">
+      <x:c r="G1" s="11" t="str">
         <x:v>bloomTaxonomy</x:v>
       </x:c>
-      <x:c r="H1" s="8" t="str">
+      <x:c r="H1" s="11" t="str">
         <x:v>tags</x:v>
       </x:c>
-      <x:c r="I1" s="8" t="str">
+      <x:c r="I1" s="11" t="str">
         <x:v>subjects</x:v>
       </x:c>
-      <x:c r="J1" s="8" t="str">
+      <x:c r="J1" s="11" t="str">
         <x:v>topics</x:v>
       </x:c>
-      <x:c r="K1" s="8" t="str">
+      <x:c r="K1" s="11" t="str">
         <x:v>subTopics</x:v>
       </x:c>
-      <x:c r="L1" s="8" t="str">
+      <x:c r="L1" s="11" t="str">
         <x:v>companies</x:v>
       </x:c>
-      <x:c r="M1" s="8" t="str">
+      <x:c r="M1" s="11" t="str">
         <x:v>option1</x:v>
       </x:c>
-      <x:c r="N1" s="8" t="str">
+      <x:c r="N1" s="11" t="str">
         <x:v>option2</x:v>
       </x:c>
-      <x:c r="O1" s="8" t="str">
+      <x:c r="O1" s="11" t="str">
         <x:v>option3</x:v>
       </x:c>
-      <x:c r="P1" s="8" t="str">
+      <x:c r="P1" s="11" t="str">
         <x:v>option4</x:v>
       </x:c>
-      <x:c r="Q1" s="8" t="str">
+      <x:c r="Q1" s="11" t="str">
         <x:v>answer</x:v>
       </x:c>
     </x:row>
@@ -452,7 +468,7 @@
 Which loop should the scanner use to visit every ID cleanly?</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
-        <x:v>A for loop is best when the program already has a sequence of items to visit. Here, the roll-number list decides exactly what must be processed, so Python can take one roll number at a time without a manually managed counter.</x:v>
+        <x:v>A `for` loop is best when the program already has a sequence of package IDs to visit. Python can take one ID at a time without a manually managed counter.</x:v>
       </x:c>
       <x:c r="D2" s="9" t="n">
         <x:v>1</x:v>
@@ -480,16 +496,16 @@
       </x:c>
       <x:c r="L2" s="9"/>
       <x:c r="M2" s="9" t="str">
-        <x:v>A recursive function, because attendance needs repetition</x:v>
+        <x:v>A recursive function that repeatedly rescans the package-ID list until an external stop condition is met</x:v>
       </x:c>
       <x:c r="N2" s="9" t="str">
-        <x:v>An if statement for each possible roll number</x:v>
+        <x:v>A separate `if` statement for every possible package ID</x:v>
       </x:c>
       <x:c r="O2" s="9" t="str">
         <x:v>A while loop that runs forever and stops manually</x:v>
       </x:c>
       <x:c r="P2" s="9" t="str">
-        <x:v>A for loop that iterates through the roll-number list</x:v>
+        <x:v>A `for` loop that iterates through the package-ID list</x:v>
       </x:c>
       <x:c r="Q2" s="9" t="n">
         <x:v>4</x:v>
@@ -719,18 +735,18 @@
         <x:v>Python - MCQ - 4.1.6</x:v>
       </x:c>
       <x:c r="B7" s="9" t="str">
-        <x:v>A scholarship checker scans scores in order and should stop as soon as it finds the first score of 90 or above.
-```python
-scores = [72, 88, 91, 95]
-for score in scores:
-    if score &gt;= 90:
-        print(score)
+        <x:v>A quality monitor scans sensor readings in order and should stop as soon as it finds the first reading of 90 or above.
+```python
+readings = [72, 88, 91, 95]
+for reading in readings:
+    if reading &gt;= 90:
+        print(reading)
         break
 ```
-Which score will the checker display as the first qualifying score?</x:v>
+Which reading will the monitor identify as the first threshold breach?</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
-        <x:v>The loop checks scores in order. 72 and 88 do not qualify. 91 qualifies, so it is printed and `break` stops the loop before 95 is checked.</x:v>
+        <x:v>The loop checks readings in order. 72 and 88 are below the threshold. 91 qualifies, so it is reported and `break` stops the loop before 95 is checked.</x:v>
       </x:c>
       <x:c r="D7" s="9" t="n">
         <x:v>1</x:v>
@@ -2569,7 +2585,7 @@
 If the service uses one loop for customers and a nested loop for products, how many comparisons will it perform?</x:v>
       </x:c>
       <x:c r="C39" s="9" t="str">
-        <x:v>The inner loop runs 100 times for each of the 100 users, so the total is 100 x 100 = 10,000 comparisons.</x:v>
+        <x:v>The inner loop runs 100 times for each of the 100 customers, so the total is 100 × 100 = 10,000 product comparisons.</x:v>
       </x:c>
       <x:c r="D39" s="9" t="n">
         <x:v>1</x:v>
@@ -2733,7 +2749,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b859afc40aa42b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64431399a67e4bb9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/content/Question Bank/MCQ/Unit 4 - Looping/Unit 4 - Looping - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Unit 4 - Looping/Unit 4 - Looping - MCQ.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 4" sheetId="1" r:id="R4d3313ba56aa42bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 4" sheetId="1" r:id="Raf8fe5dcc7b9493c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -30,12 +30,32 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -59,7 +79,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -90,6 +110,18 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -407,55 +439,55 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" customHeight="1">
-      <x:c r="A1" s="11" t="str">
+      <x:c r="A1" s="15" t="str">
         <x:v>title</x:v>
       </x:c>
-      <x:c r="B1" s="11" t="str">
+      <x:c r="B1" s="15" t="str">
         <x:v>description</x:v>
       </x:c>
-      <x:c r="C1" s="11" t="str">
+      <x:c r="C1" s="15" t="str">
         <x:v>explanation</x:v>
       </x:c>
-      <x:c r="D1" s="11" t="str">
+      <x:c r="D1" s="15" t="str">
         <x:v>score</x:v>
       </x:c>
-      <x:c r="E1" s="11" t="str">
+      <x:c r="E1" s="15" t="str">
         <x:v>status</x:v>
       </x:c>
-      <x:c r="F1" s="11" t="str">
+      <x:c r="F1" s="15" t="str">
         <x:v>difficulty</x:v>
       </x:c>
-      <x:c r="G1" s="11" t="str">
+      <x:c r="G1" s="15" t="str">
         <x:v>bloomTaxonomy</x:v>
       </x:c>
-      <x:c r="H1" s="11" t="str">
+      <x:c r="H1" s="15" t="str">
         <x:v>tags</x:v>
       </x:c>
-      <x:c r="I1" s="11" t="str">
+      <x:c r="I1" s="15" t="str">
         <x:v>subjects</x:v>
       </x:c>
-      <x:c r="J1" s="11" t="str">
+      <x:c r="J1" s="15" t="str">
         <x:v>topics</x:v>
       </x:c>
-      <x:c r="K1" s="11" t="str">
+      <x:c r="K1" s="15" t="str">
         <x:v>subTopics</x:v>
       </x:c>
-      <x:c r="L1" s="11" t="str">
+      <x:c r="L1" s="15" t="str">
         <x:v>companies</x:v>
       </x:c>
-      <x:c r="M1" s="11" t="str">
+      <x:c r="M1" s="15" t="str">
         <x:v>option1</x:v>
       </x:c>
-      <x:c r="N1" s="11" t="str">
+      <x:c r="N1" s="15" t="str">
         <x:v>option2</x:v>
       </x:c>
-      <x:c r="O1" s="11" t="str">
+      <x:c r="O1" s="15" t="str">
         <x:v>option3</x:v>
       </x:c>
-      <x:c r="P1" s="11" t="str">
+      <x:c r="P1" s="15" t="str">
         <x:v>option4</x:v>
       </x:c>
-      <x:c r="Q1" s="11" t="str">
+      <x:c r="Q1" s="15" t="str">
         <x:v>answer</x:v>
       </x:c>
     </x:row>
@@ -585,7 +617,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F4" s="9" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G4" s="9" t="str">
         <x:v>apply</x:v>
@@ -637,7 +669,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F5" s="9" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G5" s="9" t="str">
         <x:v>understand</x:v>
@@ -696,7 +728,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F6" s="9" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G6" s="9" t="str">
         <x:v>apply</x:v>
@@ -816,7 +848,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F8" s="9" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G8" s="9" t="str">
         <x:v>understand</x:v>
@@ -937,7 +969,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F10" s="9" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G10" s="9" t="str">
         <x:v>analyze</x:v>
@@ -989,7 +1021,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F11" s="9" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G11" s="9" t="str">
         <x:v>analyze</x:v>
@@ -1046,7 +1078,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F12" s="9" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G12" s="9" t="str">
         <x:v>apply</x:v>
@@ -1104,7 +1136,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F13" s="9" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G13" s="9" t="str">
         <x:v>analyze</x:v>
@@ -1218,7 +1250,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F15" s="9" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G15" s="9" t="str">
         <x:v>analyze</x:v>
@@ -1389,7 +1421,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F18" s="9" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G18" s="9" t="str">
         <x:v>analyze</x:v>
@@ -1449,7 +1481,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F19" s="9" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G19" s="9" t="str">
         <x:v>apply</x:v>
@@ -1505,7 +1537,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F20" s="9" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G20" s="9" t="str">
         <x:v>analyze</x:v>
@@ -1557,7 +1589,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F21" s="9" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G21" s="9" t="str">
         <x:v>apply</x:v>
@@ -1737,7 +1769,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F24" s="9" t="str">
-        <x:v>hard</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G24" s="9" t="str">
         <x:v>apply</x:v>
@@ -1847,7 +1879,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F26" s="9" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G26" s="9" t="str">
         <x:v>analyze</x:v>
@@ -2129,7 +2161,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F31" s="9" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G31" s="9" t="str">
         <x:v>analyze</x:v>
@@ -2479,7 +2511,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F37" s="9" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G37" s="9" t="str">
         <x:v>apply</x:v>
@@ -2542,7 +2574,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F38" s="9" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G38" s="9" t="str">
         <x:v>analyze</x:v>
@@ -2576,16 +2608,15 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="66" hidden="0" customHeight="1">
+    <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A39" s="9" t="str">
         <x:v>Python - MCQ - 4.2.28</x:v>
       </x:c>
       <x:c r="B39" s="9" t="str">
-        <x:v>A product-matching service compares every customer against every product. There are 100 customers and 100 products.
-If the service uses one loop for customers and a nested loop for products, how many comparisons will it perform?</x:v>
+        <x:v>A loop should process indexes 0 through `len(items) - 1`, but it uses `while i &lt;= len(items)`. Which boundary test most directly exposes the bug?</x:v>
       </x:c>
       <x:c r="C39" s="9" t="str">
-        <x:v>The inner loop runs 100 times for each of the 100 customers, so the total is 100 × 100 = 10,000 product comparisons.</x:v>
+        <x:v>A one-item list reaches `i == 1`; the condition still passes and the code attempts `items[1]`, exposing the off-by-one error.</x:v>
       </x:c>
       <x:c r="D39" s="9" t="n">
         <x:v>1</x:v>
@@ -2594,7 +2625,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F39" s="9" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G39" s="9" t="str">
         <x:v>analyze</x:v>
@@ -2609,41 +2640,34 @@
         <x:v>loops-and-iteration</x:v>
       </x:c>
       <x:c r="K39" s="9" t="str">
-        <x:v>nested-loops</x:v>
+        <x:v>loop-testing</x:v>
       </x:c>
       <x:c r="L39" s="9"/>
       <x:c r="M39" s="9" t="str">
-        <x:v>100</x:v>
+        <x:v>Run it only with a hundred-item list and inspect the first element</x:v>
       </x:c>
       <x:c r="N39" s="9" t="str">
-        <x:v>200</x:v>
+        <x:v>Run it with integers instead of strings, which does not change the invalid boundary</x:v>
       </x:c>
       <x:c r="O39" s="9" t="str">
-        <x:v>10,000</x:v>
+        <x:v>Run it with a one-item list and observe the access at index 1</x:v>
       </x:c>
       <x:c r="P39" s="9" t="str">
-        <x:v>1,000 — incorrectly multiplying one dimension by only ten passes</x:v>
+        <x:v>Rename `i` to `index` without changing the loop condition</x:v>
       </x:c>
       <x:c r="Q39" s="9" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="132" hidden="0" customHeight="1">
+    <x:row r="40" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A40" s="9" t="str">
         <x:v>Python - MCQ - 4.2.29</x:v>
       </x:c>
       <x:c r="B40" s="9" t="str">
-        <x:v>A terminal pattern currently grows by row.
-```python
-for row in range(1, 4):
-    for col in range(row):
-        print("#", end="")
-    print()
-```
-The new requirement is to show exactly 3 hashes on every row for 3 rows. What should the developer change?</x:v>
+        <x:v>Compare two implementations that visit every order once: A uses `for order in orders`; B uses a manually updated index in a `while` loop. No index is otherwise needed. Which implementation is better and why?</x:v>
       </x:c>
       <x:c r="C40" s="9" t="str">
-        <x:v>The current inner range depends on `row`, so the width changes. Using `range(3)` for the inner loop prints exactly three hashes on every row.</x:v>
+        <x:v>Direct iteration states the requirement clearly and removes the extra counter and boundary condition that could fail.</x:v>
       </x:c>
       <x:c r="D40" s="9" t="n">
         <x:v>1</x:v>
@@ -2655,7 +2679,7 @@
         <x:v>hard</x:v>
       </x:c>
       <x:c r="G40" s="9" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H40" s="9" t="str">
         <x:v>python - Set 2</x:v>
@@ -2667,43 +2691,34 @@
         <x:v>loops-and-iteration</x:v>
       </x:c>
       <x:c r="K40" s="9" t="str">
-        <x:v>nested-loops</x:v>
+        <x:v>choosing-loops</x:v>
       </x:c>
       <x:c r="L40" s="9"/>
       <x:c r="M40" s="9" t="str">
-        <x:v>Change `end=""` to `end="\n"`</x:v>
+        <x:v>B, because every collection loop must expose a numeric index</x:v>
       </x:c>
       <x:c r="N40" s="9" t="str">
-        <x:v>Change the inner loop to `for col in range(3):`</x:v>
+        <x:v>A, because direct iteration avoids an unnecessary counter and boundary check</x:v>
       </x:c>
       <x:c r="O40" s="9" t="str">
-        <x:v>Remove the final `print()`</x:v>
+        <x:v>B, because `while` automatically prevents off-by-one errors under every possible update</x:v>
       </x:c>
       <x:c r="P40" s="9" t="str">
-        <x:v>Change the outer loop to `for row in range(row):`</x:v>
+        <x:v>They are identical in maintainability because both use Python syntax</x:v>
       </x:c>
       <x:c r="Q40" s="9" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="158.39999389648438" hidden="0" customHeight="1">
+    <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A41" s="9" t="str">
         <x:v>Python - MCQ - 4.2.30</x:v>
       </x:c>
       <x:c r="B41" s="9" t="str">
-        <x:v>A payment checker should confirm that every bill amount is positive.
-```python
-amounts = [200, 150, 0]
-all_positive = True
-for amount in amounts:
-    if amount &lt;= 0:
-        all_positive = False
-        break
-```
-After the payment checker reaches the zero amount, what final value will it store in `all_positive`?</x:v>
+        <x:v>A retry loop works except that `attempts` never changes. What is the smallest correct change that makes failure stop after three tries?</x:v>
       </x:c>
       <x:c r="C41" s="9" t="str">
-        <x:v>The loop reaches amount 0, which is not positive. It sets `all_positive` to False and breaks, so the final value is False.</x:v>
+        <x:v>Incrementing the existing counter once after each failed attempt preserves the design and makes the loop condition eventually become false.</x:v>
       </x:c>
       <x:c r="D41" s="9" t="n">
         <x:v>1</x:v>
@@ -2727,20 +2742,20 @@
         <x:v>loops-and-iteration</x:v>
       </x:c>
       <x:c r="K41" s="9" t="str">
-        <x:v>common-loop-patterns</x:v>
+        <x:v>while-loops</x:v>
       </x:c>
       <x:c r="L41" s="9"/>
       <x:c r="M41" s="9" t="str">
-        <x:v>True, because the first two values are positive</x:v>
+        <x:v>Replace the entire retry feature with recursion and remove the existing counter and condition</x:v>
       </x:c>
       <x:c r="N41" s="9" t="str">
-        <x:v>The code raises an error because lists cannot contain 0</x:v>
+        <x:v>Change the limit from 3 to 30</x:v>
       </x:c>
       <x:c r="O41" s="9" t="str">
-        <x:v>False, because 0 fails the `amount &lt;= 0` check</x:v>
+        <x:v>Add `attempts += 1` after each failed attempt</x:v>
       </x:c>
       <x:c r="P41" s="9" t="str">
-        <x:v>True, because `break` changes False back to True</x:v>
+        <x:v>Add another `print()` inside the loop</x:v>
       </x:c>
       <x:c r="Q41" s="9" t="n">
         <x:v>3</x:v>
@@ -2749,7 +2764,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64431399a67e4bb9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85d7433dd4514566"/>
   </x:tableParts>
 </x:worksheet>
 </file>